--- a/GUA/Waste/A1_Outputs/A-O_Demand.xlsx
+++ b/GUA/Waste/A1_Outputs/A-O_Demand.xlsx
@@ -1,21 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IgnacioAlfaroCorrale\Desktop\Models_running\GUA_Modelos_Sectoriales_2024_11_25\M1_Waste\A1_Outputs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IgnacioAlfaroCorrale\Desktop\Models_running\0_guatemala_2025\Waste_GUA_v1_2025\A1_Outputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27B35535-4845-4489-B3B9-482101BBC0E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{326D52CD-07E2-4FAD-8C25-37E0329E6A15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-45" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Demand_Projection" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191028"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Demand_Projection!$A$1:$AO$1</definedName>
+  </definedNames>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -33,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="29">
   <si>
     <t>Demand/Share</t>
   </si>
@@ -62,22 +65,64 @@
     <t>Demand</t>
   </si>
   <si>
-    <t>E5_TSWTSW</t>
+    <t>E5TSWTSW</t>
+  </si>
+  <si>
+    <t>E5TSWLANDFILL_ELEC</t>
   </si>
   <si>
     <t>Demand Total solid waste Total solid waste</t>
   </si>
   <si>
+    <t>Demand Total solid waste Methane recovery in landfill to generate electricity</t>
+  </si>
+  <si>
     <t>not needed</t>
   </si>
   <si>
-    <t>Demand Total waste water Total waste water</t>
-  </si>
-  <si>
-    <t>E5_TWWTWW</t>
-  </si>
-  <si>
-    <t>Otro</t>
+    <t>User defined</t>
+  </si>
+  <si>
+    <t>E5TSWIND_SW</t>
+  </si>
+  <si>
+    <t>Demand Total solid waste Industrial solid waste</t>
+  </si>
+  <si>
+    <t>Demand Total solid waste Carbon dioxide from burning methane</t>
+  </si>
+  <si>
+    <t>E5TSWCO2_CH4_BURN</t>
+  </si>
+  <si>
+    <t>E5WWDWW_DC</t>
+  </si>
+  <si>
+    <t>Demand Waste water Domestic wastewater (degradable organic component)</t>
+  </si>
+  <si>
+    <t>E5WWDWW_N</t>
+  </si>
+  <si>
+    <t>Demand Waste water Domestic wastewater (nitrogen)</t>
+  </si>
+  <si>
+    <t>E5WWIWW</t>
+  </si>
+  <si>
+    <t>Demand Waste water Industrial waste water</t>
+  </si>
+  <si>
+    <t>E5TSWCOMPOST_DOM</t>
+  </si>
+  <si>
+    <t>Demand Total solid waste Domestic compost</t>
+  </si>
+  <si>
+    <t>E5TSWCOMPOST_COFFEE</t>
+  </si>
+  <si>
+    <t>Demand Total solid waste Agroindustrial compost</t>
   </si>
 </sst>
 </file>
@@ -85,9 +130,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -103,15 +148,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -120,12 +158,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -134,34 +178,121 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
+      <left style="medium">
+        <color indexed="64"/>
       </left>
-      <right style="thin">
-        <color auto="1"/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
       </right>
-      <top style="thin">
-        <color auto="1"/>
+      <top style="medium">
+        <color indexed="64"/>
       </top>
-      <bottom style="thin">
-        <color auto="1"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Millares 2 2" xfId="1" xr:uid="{42036F18-CEC7-4ED0-A006-4330C4E21315}"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -464,410 +595,1277 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AO3"/>
-  <sheetFormatPr defaultColWidth="9.21875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:AO10"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="21.77734375" bestFit="1" customWidth="1"/>
-    <col min="9" max="41" width="13.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="69.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="23.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="41" width="11.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:41" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+    <row r="1" spans="1:41" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1">
+      <c r="I1" s="8">
         <v>2018</v>
       </c>
-      <c r="J1" s="1">
+      <c r="J1" s="8">
         <v>2019</v>
       </c>
-      <c r="K1" s="1">
+      <c r="K1" s="8">
         <v>2020</v>
       </c>
-      <c r="L1" s="1">
+      <c r="L1" s="8">
         <v>2021</v>
       </c>
-      <c r="M1" s="1">
+      <c r="M1" s="8">
         <v>2022</v>
       </c>
-      <c r="N1" s="1">
+      <c r="N1" s="8">
         <v>2023</v>
       </c>
-      <c r="O1" s="1">
+      <c r="O1" s="8">
         <v>2024</v>
       </c>
-      <c r="P1" s="1">
+      <c r="P1" s="8">
         <v>2025</v>
       </c>
-      <c r="Q1" s="1">
+      <c r="Q1" s="8">
         <v>2026</v>
       </c>
-      <c r="R1" s="1">
+      <c r="R1" s="8">
         <v>2027</v>
       </c>
-      <c r="S1" s="1">
+      <c r="S1" s="8">
         <v>2028</v>
       </c>
-      <c r="T1" s="1">
+      <c r="T1" s="8">
         <v>2029</v>
       </c>
-      <c r="U1" s="1">
+      <c r="U1" s="8">
         <v>2030</v>
       </c>
-      <c r="V1" s="1">
+      <c r="V1" s="8">
         <v>2031</v>
       </c>
-      <c r="W1" s="1">
+      <c r="W1" s="8">
         <v>2032</v>
       </c>
-      <c r="X1" s="1">
+      <c r="X1" s="8">
         <v>2033</v>
       </c>
-      <c r="Y1" s="1">
+      <c r="Y1" s="8">
         <v>2034</v>
       </c>
-      <c r="Z1" s="1">
+      <c r="Z1" s="8">
         <v>2035</v>
       </c>
-      <c r="AA1" s="1">
+      <c r="AA1" s="8">
         <v>2036</v>
       </c>
-      <c r="AB1" s="1">
+      <c r="AB1" s="8">
         <v>2037</v>
       </c>
-      <c r="AC1" s="1">
+      <c r="AC1" s="8">
         <v>2038</v>
       </c>
-      <c r="AD1" s="1">
+      <c r="AD1" s="8">
         <v>2039</v>
       </c>
-      <c r="AE1" s="1">
+      <c r="AE1" s="8">
         <v>2040</v>
       </c>
-      <c r="AF1" s="1">
+      <c r="AF1" s="8">
         <v>2041</v>
       </c>
-      <c r="AG1" s="1">
+      <c r="AG1" s="8">
         <v>2042</v>
       </c>
-      <c r="AH1" s="1">
+      <c r="AH1" s="8">
         <v>2043</v>
       </c>
-      <c r="AI1" s="1">
+      <c r="AI1" s="8">
         <v>2044</v>
       </c>
-      <c r="AJ1" s="1">
+      <c r="AJ1" s="8">
         <v>2045</v>
       </c>
-      <c r="AK1" s="1">
+      <c r="AK1" s="8">
         <v>2046</v>
       </c>
-      <c r="AL1" s="1">
+      <c r="AL1" s="8">
         <v>2047</v>
       </c>
-      <c r="AM1" s="1">
+      <c r="AM1" s="8">
         <v>2048</v>
       </c>
-      <c r="AN1" s="1">
+      <c r="AN1" s="8">
         <v>2049</v>
       </c>
-      <c r="AO1" s="1">
+      <c r="AO1" s="9">
         <v>2050</v>
       </c>
     </row>
     <row r="2" spans="1:41" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="C2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="C2" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="E2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H2">
-        <v>0</v>
-      </c>
-      <c r="I2" s="2">
-        <v>4.4067105605846235</v>
-      </c>
-      <c r="J2" s="2">
-        <v>4.5879976694134683</v>
-      </c>
-      <c r="K2" s="2">
-        <v>4.7692847782423113</v>
-      </c>
-      <c r="L2" s="2">
-        <v>4.950571887071157</v>
-      </c>
-      <c r="M2" s="2">
-        <v>5.1318589959000009</v>
-      </c>
-      <c r="N2" s="2">
-        <v>5.3268696378479996</v>
-      </c>
-      <c r="O2" s="2">
-        <v>5.5292906840862202</v>
-      </c>
-      <c r="P2" s="2">
-        <v>5.7394037300815004</v>
-      </c>
-      <c r="Q2" s="2">
-        <v>5.9575010718245904</v>
-      </c>
-      <c r="R2" s="2">
-        <v>6.1838861125539299</v>
-      </c>
-      <c r="S2" s="2">
-        <v>6.4188737848309803</v>
-      </c>
-      <c r="T2" s="2">
-        <v>6.6627909886545602</v>
-      </c>
-      <c r="U2" s="2">
-        <v>6.9159770462234302</v>
-      </c>
-      <c r="V2" s="2">
-        <v>7.1787841739799196</v>
-      </c>
-      <c r="W2" s="2">
-        <v>7.4515779725911599</v>
-      </c>
-      <c r="X2" s="2">
-        <v>7.73473793554962</v>
-      </c>
-      <c r="Y2" s="2">
-        <v>8.0286579771005098</v>
-      </c>
-      <c r="Z2" s="2">
-        <v>8.3337469802303303</v>
-      </c>
-      <c r="AA2" s="2">
-        <v>8.6504293654790807</v>
-      </c>
-      <c r="AB2" s="2">
-        <v>8.9791456813672905</v>
-      </c>
-      <c r="AC2" s="2">
-        <v>9.3203532172592407</v>
-      </c>
-      <c r="AD2" s="2">
-        <v>9.6745266395151006</v>
-      </c>
-      <c r="AE2" s="2">
-        <v>10.0421586518166</v>
-      </c>
-      <c r="AF2" s="2">
-        <v>10.423760680585699</v>
-      </c>
-      <c r="AG2" s="2">
-        <v>10.8198635864479</v>
-      </c>
-      <c r="AH2" s="2">
-        <v>11.2310184027329</v>
-      </c>
-      <c r="AI2" s="2">
-        <v>11.657797102036801</v>
-      </c>
-      <c r="AJ2" s="2">
-        <v>12.1007933919142</v>
-      </c>
-      <c r="AK2" s="2">
-        <v>12.560623540806899</v>
-      </c>
-      <c r="AL2" s="2">
-        <v>13.0379272353576</v>
-      </c>
-      <c r="AM2" s="2">
-        <v>13.5333684703012</v>
-      </c>
-      <c r="AN2" s="2">
-        <v>14.0476364721726</v>
-      </c>
-      <c r="AO2" s="2">
-        <v>14.581446658115199</v>
+      <c r="D2" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" s="11">
+        <v>0</v>
+      </c>
+      <c r="I2" s="21">
+        <v>2.8971</v>
+      </c>
+      <c r="J2" s="21">
+        <v>3.0177</v>
+      </c>
+      <c r="K2" s="21">
+        <v>3.1582000000000003</v>
+      </c>
+      <c r="L2" s="21">
+        <v>3.3022</v>
+      </c>
+      <c r="M2" s="21">
+        <v>3.4495</v>
+      </c>
+      <c r="N2" s="21">
+        <v>3.5806</v>
+      </c>
+      <c r="O2" s="21">
+        <v>3.7167000000000003</v>
+      </c>
+      <c r="P2" s="21">
+        <v>3.8578999999999999</v>
+      </c>
+      <c r="Q2" s="21">
+        <v>4.0043999999999995</v>
+      </c>
+      <c r="R2" s="21">
+        <v>4.1566000000000001</v>
+      </c>
+      <c r="S2" s="21">
+        <v>4.3147000000000002</v>
+      </c>
+      <c r="T2" s="21">
+        <v>4.4786000000000001</v>
+      </c>
+      <c r="U2" s="21">
+        <v>4.6487999999999996</v>
+      </c>
+      <c r="V2" s="21">
+        <v>4.8254999999999999</v>
+      </c>
+      <c r="W2" s="21">
+        <v>5.0087999999999999</v>
+      </c>
+      <c r="X2" s="21">
+        <v>5.1990999999999996</v>
+      </c>
+      <c r="Y2" s="21">
+        <v>5.3967000000000001</v>
+      </c>
+      <c r="Z2" s="21">
+        <v>5.6017000000000001</v>
+      </c>
+      <c r="AA2" s="21">
+        <v>5.8147000000000002</v>
+      </c>
+      <c r="AB2" s="21">
+        <v>6.0356000000000005</v>
+      </c>
+      <c r="AC2" s="21">
+        <v>6.264899999999999</v>
+      </c>
+      <c r="AD2" s="21">
+        <v>6.5030000000000001</v>
+      </c>
+      <c r="AE2" s="21">
+        <v>6.7500999999999998</v>
+      </c>
+      <c r="AF2" s="21">
+        <v>7.0066000000000006</v>
+      </c>
+      <c r="AG2" s="21">
+        <v>7.2728999999999999</v>
+      </c>
+      <c r="AH2" s="21">
+        <v>7.549199999999999</v>
+      </c>
+      <c r="AI2" s="21">
+        <v>7.8361000000000001</v>
+      </c>
+      <c r="AJ2" s="21">
+        <v>8.1339000000000006</v>
+      </c>
+      <c r="AK2" s="21">
+        <v>8.4428999999999998</v>
+      </c>
+      <c r="AL2" s="21">
+        <v>8.7637999999999998</v>
+      </c>
+      <c r="AM2" s="21">
+        <v>9.0968</v>
+      </c>
+      <c r="AN2" s="21">
+        <v>9.442499999999999</v>
+      </c>
+      <c r="AO2" s="22">
+        <v>9.8013000000000012</v>
       </c>
     </row>
     <row r="3" spans="1:41" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="B3" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="D3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3" t="s">
+      <c r="D3" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3" s="2">
-        <v>1.7654706</v>
-      </c>
-      <c r="J3" s="2">
-        <v>1.8325584827999994</v>
-      </c>
-      <c r="K3" s="2">
-        <v>1.9021957051464</v>
-      </c>
-      <c r="L3" s="2">
-        <v>1.9744791419419614</v>
-      </c>
-      <c r="M3" s="2">
-        <v>2.0495093493357563</v>
-      </c>
-      <c r="N3" s="2">
-        <v>2.1273907046105127</v>
-      </c>
-      <c r="O3" s="2">
-        <v>2.2082315513857118</v>
-      </c>
-      <c r="P3" s="2">
-        <v>2.2921443503383712</v>
-      </c>
-      <c r="Q3" s="2">
-        <v>2.3792458356512318</v>
-      </c>
-      <c r="R3" s="2">
-        <v>2.4696571774059741</v>
-      </c>
-      <c r="S3" s="2">
-        <v>2.5635041501474025</v>
-      </c>
-      <c r="T3" s="2">
-        <v>2.660917307853008</v>
-      </c>
-      <c r="U3" s="2">
-        <v>2.7620321655514184</v>
-      </c>
-      <c r="V3" s="2">
-        <v>2.8669893878423722</v>
-      </c>
-      <c r="W3" s="2">
-        <v>2.9759349845803835</v>
-      </c>
-      <c r="X3" s="2">
-        <v>3.0890205139944391</v>
-      </c>
-      <c r="Y3" s="2">
-        <v>3.2064032935262263</v>
-      </c>
-      <c r="Z3" s="2">
-        <v>3.3282466186802218</v>
-      </c>
-      <c r="AA3" s="2">
-        <v>3.4547199901900707</v>
-      </c>
-      <c r="AB3" s="2">
-        <v>3.5859993498172962</v>
-      </c>
-      <c r="AC3" s="2">
-        <v>3.7222673251103537</v>
-      </c>
-      <c r="AD3" s="2">
-        <v>3.8637134834645463</v>
-      </c>
-      <c r="AE3" s="2">
-        <v>4.0105345958362006</v>
-      </c>
-      <c r="AF3" s="2">
-        <v>4.1629349104779765</v>
-      </c>
-      <c r="AG3" s="2">
-        <v>4.321126437076142</v>
-      </c>
-      <c r="AH3" s="2">
-        <v>4.4853292416850348</v>
-      </c>
-      <c r="AI3" s="2">
-        <v>4.6557717528690636</v>
-      </c>
-      <c r="AJ3" s="2">
-        <v>4.8326910794780904</v>
-      </c>
-      <c r="AK3" s="2">
-        <v>5.0163333404982557</v>
-      </c>
-      <c r="AL3" s="2">
-        <v>5.2069540074371909</v>
-      </c>
-      <c r="AM3" s="2">
-        <v>5.404818259719808</v>
-      </c>
-      <c r="AN3" s="2">
-        <v>5.6102013535891126</v>
-      </c>
-      <c r="AO3" s="2">
-        <v>5.8233890050255299</v>
+      <c r="H3" s="16">
+        <v>0</v>
+      </c>
+      <c r="I3" s="19">
+        <v>0</v>
+      </c>
+      <c r="J3" s="19">
+        <v>0</v>
+      </c>
+      <c r="K3" s="19">
+        <v>0</v>
+      </c>
+      <c r="L3" s="19">
+        <v>0</v>
+      </c>
+      <c r="M3" s="19">
+        <v>0</v>
+      </c>
+      <c r="N3" s="19">
+        <v>0</v>
+      </c>
+      <c r="O3" s="19">
+        <v>0</v>
+      </c>
+      <c r="P3" s="19">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="19">
+        <v>0</v>
+      </c>
+      <c r="R3" s="19">
+        <v>0</v>
+      </c>
+      <c r="S3" s="19">
+        <v>0</v>
+      </c>
+      <c r="T3" s="19">
+        <v>0</v>
+      </c>
+      <c r="U3" s="19">
+        <v>0</v>
+      </c>
+      <c r="V3" s="19">
+        <v>0</v>
+      </c>
+      <c r="W3" s="19">
+        <v>0</v>
+      </c>
+      <c r="X3" s="19">
+        <v>0</v>
+      </c>
+      <c r="Y3" s="19">
+        <v>0</v>
+      </c>
+      <c r="Z3" s="19">
+        <v>0</v>
+      </c>
+      <c r="AA3" s="19">
+        <v>0</v>
+      </c>
+      <c r="AB3" s="19">
+        <v>0</v>
+      </c>
+      <c r="AC3" s="19">
+        <v>0</v>
+      </c>
+      <c r="AD3" s="19">
+        <v>0</v>
+      </c>
+      <c r="AE3" s="19">
+        <v>0</v>
+      </c>
+      <c r="AF3" s="19">
+        <v>0</v>
+      </c>
+      <c r="AG3" s="19">
+        <v>0</v>
+      </c>
+      <c r="AH3" s="19">
+        <v>0</v>
+      </c>
+      <c r="AI3" s="19">
+        <v>0</v>
+      </c>
+      <c r="AJ3" s="19">
+        <v>0</v>
+      </c>
+      <c r="AK3" s="19">
+        <v>0</v>
+      </c>
+      <c r="AL3" s="19">
+        <v>0</v>
+      </c>
+      <c r="AM3" s="19">
+        <v>0</v>
+      </c>
+      <c r="AN3" s="19">
+        <v>0</v>
+      </c>
+      <c r="AO3" s="20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:41" x14ac:dyDescent="0.3">
+      <c r="A4" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="H4" s="16">
+        <v>0</v>
+      </c>
+      <c r="I4" s="19">
+        <v>0</v>
+      </c>
+      <c r="J4" s="19">
+        <v>0</v>
+      </c>
+      <c r="K4" s="19">
+        <v>0</v>
+      </c>
+      <c r="L4" s="19">
+        <v>0</v>
+      </c>
+      <c r="M4" s="19">
+        <v>0</v>
+      </c>
+      <c r="N4" s="19">
+        <v>0</v>
+      </c>
+      <c r="O4" s="19">
+        <v>0</v>
+      </c>
+      <c r="P4" s="19">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="19">
+        <v>0</v>
+      </c>
+      <c r="R4" s="19">
+        <v>0</v>
+      </c>
+      <c r="S4" s="19">
+        <v>0</v>
+      </c>
+      <c r="T4" s="19">
+        <v>0</v>
+      </c>
+      <c r="U4" s="19">
+        <v>0</v>
+      </c>
+      <c r="V4" s="19">
+        <v>0</v>
+      </c>
+      <c r="W4" s="19">
+        <v>0</v>
+      </c>
+      <c r="X4" s="19">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="19">
+        <v>0</v>
+      </c>
+      <c r="Z4" s="19">
+        <v>0</v>
+      </c>
+      <c r="AA4" s="19">
+        <v>0</v>
+      </c>
+      <c r="AB4" s="19">
+        <v>0</v>
+      </c>
+      <c r="AC4" s="19">
+        <v>0</v>
+      </c>
+      <c r="AD4" s="19">
+        <v>0</v>
+      </c>
+      <c r="AE4" s="19">
+        <v>0</v>
+      </c>
+      <c r="AF4" s="19">
+        <v>0</v>
+      </c>
+      <c r="AG4" s="19">
+        <v>0</v>
+      </c>
+      <c r="AH4" s="19">
+        <v>0</v>
+      </c>
+      <c r="AI4" s="19">
+        <v>0</v>
+      </c>
+      <c r="AJ4" s="19">
+        <v>0</v>
+      </c>
+      <c r="AK4" s="19">
+        <v>0</v>
+      </c>
+      <c r="AL4" s="19">
+        <v>0</v>
+      </c>
+      <c r="AM4" s="19">
+        <v>0</v>
+      </c>
+      <c r="AN4" s="19">
+        <v>0</v>
+      </c>
+      <c r="AO4" s="20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:41" x14ac:dyDescent="0.3">
+      <c r="A5" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="H5" s="16">
+        <v>0</v>
+      </c>
+      <c r="I5" s="19">
+        <v>0</v>
+      </c>
+      <c r="J5" s="19">
+        <v>0</v>
+      </c>
+      <c r="K5" s="19">
+        <v>0</v>
+      </c>
+      <c r="L5" s="19">
+        <v>0</v>
+      </c>
+      <c r="M5" s="19">
+        <v>0</v>
+      </c>
+      <c r="N5" s="19">
+        <v>0</v>
+      </c>
+      <c r="O5" s="19">
+        <v>0</v>
+      </c>
+      <c r="P5" s="19">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="19">
+        <v>0</v>
+      </c>
+      <c r="R5" s="19">
+        <v>0</v>
+      </c>
+      <c r="S5" s="19">
+        <v>0</v>
+      </c>
+      <c r="T5" s="19">
+        <v>0</v>
+      </c>
+      <c r="U5" s="19">
+        <v>0</v>
+      </c>
+      <c r="V5" s="19">
+        <v>0</v>
+      </c>
+      <c r="W5" s="19">
+        <v>0</v>
+      </c>
+      <c r="X5" s="19">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="19">
+        <v>0</v>
+      </c>
+      <c r="Z5" s="19">
+        <v>0</v>
+      </c>
+      <c r="AA5" s="19">
+        <v>0</v>
+      </c>
+      <c r="AB5" s="19">
+        <v>0</v>
+      </c>
+      <c r="AC5" s="19">
+        <v>0</v>
+      </c>
+      <c r="AD5" s="19">
+        <v>0</v>
+      </c>
+      <c r="AE5" s="19">
+        <v>0</v>
+      </c>
+      <c r="AF5" s="19">
+        <v>0</v>
+      </c>
+      <c r="AG5" s="19">
+        <v>0</v>
+      </c>
+      <c r="AH5" s="19">
+        <v>0</v>
+      </c>
+      <c r="AI5" s="19">
+        <v>0</v>
+      </c>
+      <c r="AJ5" s="19">
+        <v>0</v>
+      </c>
+      <c r="AK5" s="19">
+        <v>0</v>
+      </c>
+      <c r="AL5" s="19">
+        <v>0</v>
+      </c>
+      <c r="AM5" s="19">
+        <v>0</v>
+      </c>
+      <c r="AN5" s="19">
+        <v>0</v>
+      </c>
+      <c r="AO5" s="20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:41" x14ac:dyDescent="0.3">
+      <c r="A6" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="G6" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="H6" s="16">
+        <v>0</v>
+      </c>
+      <c r="I6" s="19">
+        <v>8.4400000000000003E-2</v>
+      </c>
+      <c r="J6" s="19">
+        <v>8.6099999999999996E-2</v>
+      </c>
+      <c r="K6" s="19">
+        <v>8.8700000000000001E-2</v>
+      </c>
+      <c r="L6" s="19">
+        <v>9.1200000000000003E-2</v>
+      </c>
+      <c r="M6" s="19">
+        <v>9.3600000000000003E-2</v>
+      </c>
+      <c r="N6" s="19">
+        <v>9.3600000000000003E-2</v>
+      </c>
+      <c r="O6" s="19">
+        <v>9.3600000000000003E-2</v>
+      </c>
+      <c r="P6" s="19">
+        <v>9.3600000000000003E-2</v>
+      </c>
+      <c r="Q6" s="19">
+        <v>9.3600000000000003E-2</v>
+      </c>
+      <c r="R6" s="19">
+        <v>9.3600000000000003E-2</v>
+      </c>
+      <c r="S6" s="19">
+        <v>9.3600000000000003E-2</v>
+      </c>
+      <c r="T6" s="19">
+        <v>9.3600000000000003E-2</v>
+      </c>
+      <c r="U6" s="19">
+        <v>9.3600000000000003E-2</v>
+      </c>
+      <c r="V6" s="19">
+        <v>9.3600000000000003E-2</v>
+      </c>
+      <c r="W6" s="19">
+        <v>9.3600000000000003E-2</v>
+      </c>
+      <c r="X6" s="19">
+        <v>9.3600000000000003E-2</v>
+      </c>
+      <c r="Y6" s="19">
+        <v>9.3600000000000003E-2</v>
+      </c>
+      <c r="Z6" s="19">
+        <v>9.3600000000000003E-2</v>
+      </c>
+      <c r="AA6" s="19">
+        <v>9.3600000000000003E-2</v>
+      </c>
+      <c r="AB6" s="19">
+        <v>9.3600000000000003E-2</v>
+      </c>
+      <c r="AC6" s="19">
+        <v>9.3600000000000003E-2</v>
+      </c>
+      <c r="AD6" s="19">
+        <v>9.3600000000000003E-2</v>
+      </c>
+      <c r="AE6" s="19">
+        <v>9.3600000000000003E-2</v>
+      </c>
+      <c r="AF6" s="19">
+        <v>9.3600000000000003E-2</v>
+      </c>
+      <c r="AG6" s="19">
+        <v>9.3600000000000003E-2</v>
+      </c>
+      <c r="AH6" s="19">
+        <v>9.3600000000000003E-2</v>
+      </c>
+      <c r="AI6" s="19">
+        <v>9.3600000000000003E-2</v>
+      </c>
+      <c r="AJ6" s="19">
+        <v>9.3600000000000003E-2</v>
+      </c>
+      <c r="AK6" s="19">
+        <v>9.3600000000000003E-2</v>
+      </c>
+      <c r="AL6" s="19">
+        <v>9.3600000000000003E-2</v>
+      </c>
+      <c r="AM6" s="19">
+        <v>9.3600000000000003E-2</v>
+      </c>
+      <c r="AN6" s="19">
+        <v>9.3600000000000003E-2</v>
+      </c>
+      <c r="AO6" s="20">
+        <v>9.3600000000000003E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:41" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H7" s="2">
+        <v>0</v>
+      </c>
+      <c r="I7" s="17">
+        <v>0.36680000000000001</v>
+      </c>
+      <c r="J7" s="17">
+        <v>0.31790000000000002</v>
+      </c>
+      <c r="K7" s="17">
+        <v>0.316</v>
+      </c>
+      <c r="L7" s="17">
+        <v>0.31409999999999999</v>
+      </c>
+      <c r="M7" s="17">
+        <v>0.31219999999999998</v>
+      </c>
+      <c r="N7" s="17">
+        <v>0.31219999999999998</v>
+      </c>
+      <c r="O7" s="17">
+        <v>0.31219999999999998</v>
+      </c>
+      <c r="P7" s="17">
+        <v>0.31219999999999998</v>
+      </c>
+      <c r="Q7" s="17">
+        <v>0.31219999999999998</v>
+      </c>
+      <c r="R7" s="17">
+        <v>0.31219999999999998</v>
+      </c>
+      <c r="S7" s="17">
+        <v>0.31219999999999998</v>
+      </c>
+      <c r="T7" s="17">
+        <v>0.31219999999999998</v>
+      </c>
+      <c r="U7" s="17">
+        <v>0.31219999999999998</v>
+      </c>
+      <c r="V7" s="17">
+        <v>0.31219999999999998</v>
+      </c>
+      <c r="W7" s="17">
+        <v>0.31219999999999998</v>
+      </c>
+      <c r="X7" s="17">
+        <v>0.31219999999999998</v>
+      </c>
+      <c r="Y7" s="17">
+        <v>0.31219999999999998</v>
+      </c>
+      <c r="Z7" s="17">
+        <v>0.31219999999999998</v>
+      </c>
+      <c r="AA7" s="17">
+        <v>0.31219999999999998</v>
+      </c>
+      <c r="AB7" s="17">
+        <v>0.31219999999999998</v>
+      </c>
+      <c r="AC7" s="17">
+        <v>0.31219999999999998</v>
+      </c>
+      <c r="AD7" s="17">
+        <v>0.31219999999999998</v>
+      </c>
+      <c r="AE7" s="17">
+        <v>0.31219999999999998</v>
+      </c>
+      <c r="AF7" s="17">
+        <v>0.31219999999999998</v>
+      </c>
+      <c r="AG7" s="17">
+        <v>0.31219999999999998</v>
+      </c>
+      <c r="AH7" s="17">
+        <v>0.31219999999999998</v>
+      </c>
+      <c r="AI7" s="17">
+        <v>0.31219999999999998</v>
+      </c>
+      <c r="AJ7" s="17">
+        <v>0.31219999999999998</v>
+      </c>
+      <c r="AK7" s="17">
+        <v>0.31219999999999998</v>
+      </c>
+      <c r="AL7" s="17">
+        <v>0.31219999999999998</v>
+      </c>
+      <c r="AM7" s="17">
+        <v>0.31219999999999998</v>
+      </c>
+      <c r="AN7" s="17">
+        <v>0.31219999999999998</v>
+      </c>
+      <c r="AO7" s="18">
+        <v>0.31219999999999998</v>
+      </c>
+    </row>
+    <row r="8" spans="1:41" x14ac:dyDescent="0.3">
+      <c r="A8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F8" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="G8" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="H8" s="12">
+        <v>0</v>
+      </c>
+      <c r="I8" s="13">
+        <v>11.649900000000001</v>
+      </c>
+      <c r="J8" s="13">
+        <v>12.090299999999999</v>
+      </c>
+      <c r="K8" s="13">
+        <v>12.281700000000001</v>
+      </c>
+      <c r="L8" s="13">
+        <v>12.471</v>
+      </c>
+      <c r="M8" s="13">
+        <v>12.6578</v>
+      </c>
+      <c r="N8" s="13">
+        <v>13.1388</v>
+      </c>
+      <c r="O8" s="13">
+        <v>13.6381</v>
+      </c>
+      <c r="P8" s="13">
+        <v>14.1563</v>
+      </c>
+      <c r="Q8" s="13">
+        <v>14.6943</v>
+      </c>
+      <c r="R8" s="13">
+        <v>15.252599999999999</v>
+      </c>
+      <c r="S8" s="13">
+        <v>15.8322</v>
+      </c>
+      <c r="T8" s="13">
+        <v>16.433900000000001</v>
+      </c>
+      <c r="U8" s="13">
+        <v>17.058399999999999</v>
+      </c>
+      <c r="V8" s="13">
+        <v>17.706600000000002</v>
+      </c>
+      <c r="W8" s="13">
+        <v>18.3794</v>
+      </c>
+      <c r="X8" s="13">
+        <v>19.0778</v>
+      </c>
+      <c r="Y8" s="13">
+        <v>19.802800000000001</v>
+      </c>
+      <c r="Z8" s="13">
+        <v>20.555299999999999</v>
+      </c>
+      <c r="AA8" s="13">
+        <v>21.336400000000001</v>
+      </c>
+      <c r="AB8" s="13">
+        <v>22.147200000000002</v>
+      </c>
+      <c r="AC8" s="13">
+        <v>22.988800000000001</v>
+      </c>
+      <c r="AD8" s="13">
+        <v>23.862400000000001</v>
+      </c>
+      <c r="AE8" s="13">
+        <v>24.769100000000002</v>
+      </c>
+      <c r="AF8" s="13">
+        <v>25.7103</v>
+      </c>
+      <c r="AG8" s="13">
+        <v>26.6873</v>
+      </c>
+      <c r="AH8" s="13">
+        <v>27.701499999999999</v>
+      </c>
+      <c r="AI8" s="13">
+        <v>28.754100000000001</v>
+      </c>
+      <c r="AJ8" s="13">
+        <v>29.846800000000002</v>
+      </c>
+      <c r="AK8" s="13">
+        <v>30.981000000000002</v>
+      </c>
+      <c r="AL8" s="13">
+        <v>32.158200000000001</v>
+      </c>
+      <c r="AM8" s="13">
+        <v>33.380200000000002</v>
+      </c>
+      <c r="AN8" s="13">
+        <v>34.648699999999998</v>
+      </c>
+      <c r="AO8" s="14">
+        <v>35.965299999999999</v>
+      </c>
+    </row>
+    <row r="9" spans="1:41" x14ac:dyDescent="0.3">
+      <c r="A9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E9" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F9" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="G9" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="H9" s="12">
+        <v>0</v>
+      </c>
+      <c r="I9" s="13">
+        <v>102.7812</v>
+      </c>
+      <c r="J9" s="13">
+        <v>101.9675</v>
+      </c>
+      <c r="K9" s="13">
+        <v>97.687799999999996</v>
+      </c>
+      <c r="L9" s="13">
+        <v>91.2393</v>
+      </c>
+      <c r="M9" s="13">
+        <v>103.24460000000001</v>
+      </c>
+      <c r="N9" s="13">
+        <v>107.1679</v>
+      </c>
+      <c r="O9" s="13">
+        <v>111.2403</v>
+      </c>
+      <c r="P9" s="13">
+        <v>115.4674</v>
+      </c>
+      <c r="Q9" s="13">
+        <v>119.8552</v>
+      </c>
+      <c r="R9" s="13">
+        <v>124.4097</v>
+      </c>
+      <c r="S9" s="13">
+        <v>129.13720000000001</v>
+      </c>
+      <c r="T9" s="13">
+        <v>134.0444</v>
+      </c>
+      <c r="U9" s="13">
+        <v>139.13810000000001</v>
+      </c>
+      <c r="V9" s="13">
+        <v>144.4254</v>
+      </c>
+      <c r="W9" s="13">
+        <v>149.9135</v>
+      </c>
+      <c r="X9" s="13">
+        <v>155.6103</v>
+      </c>
+      <c r="Y9" s="13">
+        <v>161.52340000000001</v>
+      </c>
+      <c r="Z9" s="13">
+        <v>167.66130000000001</v>
+      </c>
+      <c r="AA9" s="13">
+        <v>174.0325</v>
+      </c>
+      <c r="AB9" s="13">
+        <v>180.64570000000001</v>
+      </c>
+      <c r="AC9" s="13">
+        <v>187.5102</v>
+      </c>
+      <c r="AD9" s="13">
+        <v>194.63560000000001</v>
+      </c>
+      <c r="AE9" s="13">
+        <v>202.0318</v>
+      </c>
+      <c r="AF9" s="13">
+        <v>209.709</v>
+      </c>
+      <c r="AG9" s="13">
+        <v>217.67789999999999</v>
+      </c>
+      <c r="AH9" s="13">
+        <v>225.94970000000001</v>
+      </c>
+      <c r="AI9" s="13">
+        <v>234.53579999999999</v>
+      </c>
+      <c r="AJ9" s="13">
+        <v>243.44810000000001</v>
+      </c>
+      <c r="AK9" s="13">
+        <v>252.69919999999999</v>
+      </c>
+      <c r="AL9" s="13">
+        <v>262.30169999999998</v>
+      </c>
+      <c r="AM9" s="13">
+        <v>272.26920000000001</v>
+      </c>
+      <c r="AN9" s="13">
+        <v>282.61540000000002</v>
+      </c>
+      <c r="AO9" s="14">
+        <v>293.35480000000001</v>
+      </c>
+    </row>
+    <row r="10" spans="1:41" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H10" s="5">
+        <v>0</v>
+      </c>
+      <c r="I10" s="5">
+        <v>20.557400000000001</v>
+      </c>
+      <c r="J10" s="5">
+        <v>10.6769</v>
+      </c>
+      <c r="K10" s="5">
+        <v>10.6136</v>
+      </c>
+      <c r="L10" s="5">
+        <v>10.5504</v>
+      </c>
+      <c r="M10" s="5">
+        <v>10.4872</v>
+      </c>
+      <c r="N10" s="5">
+        <v>10.8857</v>
+      </c>
+      <c r="O10" s="5">
+        <v>11.2994</v>
+      </c>
+      <c r="P10" s="5">
+        <v>11.7287</v>
+      </c>
+      <c r="Q10" s="5">
+        <v>12.1744</v>
+      </c>
+      <c r="R10" s="5">
+        <v>12.6371</v>
+      </c>
+      <c r="S10" s="5">
+        <v>13.1173</v>
+      </c>
+      <c r="T10" s="5">
+        <v>13.6157</v>
+      </c>
+      <c r="U10" s="5">
+        <v>14.133100000000001</v>
+      </c>
+      <c r="V10" s="5">
+        <v>14.670199999999999</v>
+      </c>
+      <c r="W10" s="5">
+        <v>15.2277</v>
+      </c>
+      <c r="X10" s="5">
+        <v>15.8063</v>
+      </c>
+      <c r="Y10" s="5">
+        <v>16.4069</v>
+      </c>
+      <c r="Z10" s="5">
+        <v>17.0304</v>
+      </c>
+      <c r="AA10" s="5">
+        <v>17.677600000000002</v>
+      </c>
+      <c r="AB10" s="5">
+        <v>18.349299999999999</v>
+      </c>
+      <c r="AC10" s="5">
+        <v>19.046600000000002</v>
+      </c>
+      <c r="AD10" s="5">
+        <v>19.770399999999999</v>
+      </c>
+      <c r="AE10" s="5">
+        <v>20.521599999999999</v>
+      </c>
+      <c r="AF10" s="5">
+        <v>21.301400000000001</v>
+      </c>
+      <c r="AG10" s="5">
+        <v>22.110900000000001</v>
+      </c>
+      <c r="AH10" s="5">
+        <v>22.9511</v>
+      </c>
+      <c r="AI10" s="5">
+        <v>23.8233</v>
+      </c>
+      <c r="AJ10" s="5">
+        <v>24.7285</v>
+      </c>
+      <c r="AK10" s="5">
+        <v>25.668199999999999</v>
+      </c>
+      <c r="AL10" s="5">
+        <v>26.643599999999999</v>
+      </c>
+      <c r="AM10" s="5">
+        <v>27.656099999999999</v>
+      </c>
+      <c r="AN10" s="5">
+        <v>28.707000000000001</v>
+      </c>
+      <c r="AO10" s="15">
+        <v>29.797899999999998</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AO1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="a1fcbaaf-06d9-47c4-b3a2-beefbc45d784">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101000360DE9767CDF0449BF75EAB371D3CB7" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="75cb9a07855af6ac97bd432464ca7c04">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="a1fcbaaf-06d9-47c4-b3a2-beefbc45d784" xmlns:ns3="081a93ea-d517-42a5-a2b7-457060aa7471" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d1676634304aab9936f6a5a5f53c7423" ns2:_="" ns3:_="">
     <xsd:import namespace="a1fcbaaf-06d9-47c4-b3a2-beefbc45d784"/>
@@ -1090,31 +2088,60 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="a1fcbaaf-06d9-47c4-b3a2-beefbc45d784">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1C4C2B2E-CDF2-4ABC-8F05-561EF1EBFAC5}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{088CE798-BF09-4C18-BA9B-2823095F0561}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="a1fcbaaf-06d9-47c4-b3a2-beefbc45d784"/>
+    <ds:schemaRef ds:uri="081a93ea-d517-42a5-a2b7-457060aa7471"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A6C6FA0-4F8E-496B-AB41-66E879B59AFF}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0D3C06FC-A061-46D7-AB8C-3A7A5EDF6442}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="081a93ea-d517-42a5-a2b7-457060aa7471"/>
+    <ds:schemaRef ds:uri="48eed89a-7418-4977-ae3a-838f0fac8ec5"/>
+    <ds:schemaRef ds:uri="416d42ac-85ec-40c4-8054-6c816fd4b6a7"/>
     <ds:schemaRef ds:uri="a1fcbaaf-06d9-47c4-b3a2-beefbc45d784"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A96E40FB-22FF-4610-BE81-4B0F43476970}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EE3DCE31-78C7-4C53-B724-B0C7214A09D5}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>